--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R45361e2301734704"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R1c6fe63283694d3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Ra56e3c88a36745b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R5c9f7a98b8d9455c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R72cfc220eefd4c3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R0afda6ead3c04ee5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R66e1d4f30468413c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R264404bc7f4c4dd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rf695e50145704a8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R12929e056b514aa9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -133,7 +133,7 @@
     <x:xf numFmtId="200" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -399,10 +399,10 @@
         <x:v>必需</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
-        <x:v>路径固定且可重复执行</x:v>
+        <x:v>路径固定且覆盖完整重建逻辑</x:v>
       </x:c>
       <x:c r="E3" s="13" t="str">
-        <x:v>数据工程师维护审计库的完整重建逻辑</x:v>
+        <x:v>数据工程师维护审计库的重建逻辑</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="38" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>路径固定</x:v>
       </x:c>
       <x:c r="E8" s="15" t="str">
-        <x:v>运营负责人确认控制量和交付状态</x:v>
+        <x:v>运营负责人查看数据范围和业务计数</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -622,26 +622,12 @@
         <x:v>audit_summary.json</x:v>
       </x:c>
       <x:c r="B9" s="13" t="str">
-        <x:v>$.status</x:v>
-      </x:c>
-      <x:c r="C9" s="17" t="str">
-        <x:v>ready</x:v>
+        <x:v>$.report_cutoff_utc</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="n">
+        <x:v>46233.583333333336</x:v>
       </x:c>
       <x:c r="D9" s="13" t="str">
-        <x:v>report_contract.json的status_values</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="42" customHeight="1">
-      <x:c r="A10" s="15" t="str">
-        <x:v>audit_summary.json</x:v>
-      </x:c>
-      <x:c r="B10" s="15" t="str">
-        <x:v>$.report_cutoff_utc</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="n">
-        <x:v>46233.583333333336</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="str">
         <x:v>report_contract.json</x:v>
       </x:c>
     </x:row>
@@ -756,20 +742,6 @@
       </x:c>
       <x:c r="D7" s="13" t="str">
         <x:v>任务Prompt</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="46" customHeight="1">
-      <x:c r="A8" s="15" t="str">
-        <x:v>审计检查</x:v>
-      </x:c>
-      <x:c r="B8" s="15" t="str">
-        <x:v>$.checks的键</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="str">
-        <x:v>all_queues_mapped；exceptions_excluded；thread_sla_roots_match</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="str">
-        <x:v>数据库内可复算关系</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1533,7 +1505,7 @@
         <x:v>可以增加不改变既定交付物的说明文档</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>附加文件不能代替规定文件或夹带预生成结果</x:v>
+        <x:v>附加文件不能代替规定交付路径</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
